--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2277"/>
+  <dimension ref="A1:D2297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="7.69140625" bestFit="1" customWidth="1" style="9" min="1" max="1"/>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>94.55</v>
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>99.45</v>
+        <v>100</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>94.25</v>
@@ -1425,7 +1425,7 @@
         <v>99.95</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>89.5</v>
+        <v>87.59999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>139.65</v>
+        <v>148</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>99.45</v>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C86" s="3" t="n">
-        <v>196</v>
+        <v>260</v>
       </c>
       <c r="D86" s="3" t="n">
         <v>98.7</v>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C113" s="3" t="n">
-        <v>192</v>
+        <v>261</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>102</v>
@@ -4734,7 +4734,7 @@
         </is>
       </c>
       <c r="C258" s="3" t="n">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="D258" s="3" t="n">
         <v>111.1</v>
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="C261" s="3" t="n">
-        <v>111</v>
+        <v>123.6</v>
       </c>
       <c r="D261" s="3" t="n">
         <v>90.5</v>
@@ -4881,7 +4881,7 @@
         <v>119.95</v>
       </c>
       <c r="D267" s="3" t="n">
-        <v>100.5</v>
+        <v>100.1</v>
       </c>
     </row>
     <row r="268">
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="C286" s="3" t="n">
-        <v>235</v>
+        <v>317</v>
       </c>
       <c r="D286" s="3" t="n">
         <v>102.2</v>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="C301" s="3" t="n">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="D301" s="3" t="n">
         <v>124.15</v>
@@ -5518,7 +5518,7 @@
         </is>
       </c>
       <c r="C307" s="3" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="D307" s="3" t="n">
         <v>109</v>
@@ -6510,7 +6510,7 @@
         </is>
       </c>
       <c r="C369" s="3" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D369" s="3" t="n">
         <v>98.90000000000001</v>
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="C392" s="3" t="n">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="D392" s="3" t="n">
         <v>110.2</v>
@@ -6894,7 +6894,7 @@
         </is>
       </c>
       <c r="C393" s="3" t="n">
-        <v>269</v>
+        <v>302</v>
       </c>
       <c r="D393" s="3" t="n">
         <v>133.1</v>
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c r="C414" s="3" t="n">
-        <v>148.55</v>
+        <v>233</v>
       </c>
       <c r="D414" s="3" t="n">
         <v>89.7</v>
@@ -7310,7 +7310,7 @@
         </is>
       </c>
       <c r="C419" s="3" t="n">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="D419" s="3" t="n">
         <v>115.5</v>
@@ -7326,7 +7326,7 @@
         </is>
       </c>
       <c r="C420" s="3" t="n">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="D420" s="3" t="n">
         <v>121</v>
@@ -7502,7 +7502,7 @@
         </is>
       </c>
       <c r="C431" s="3" t="n">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="D431" s="3" t="n">
         <v>103.15</v>
@@ -7838,7 +7838,7 @@
         </is>
       </c>
       <c r="C452" s="3" t="n">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="D452" s="3" t="n">
         <v>96.5</v>
@@ -8177,7 +8177,7 @@
         <v>123.5</v>
       </c>
       <c r="D473" s="3" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="474">
@@ -8193,7 +8193,7 @@
         <v>112.15</v>
       </c>
       <c r="D474" s="3" t="n">
-        <v>90.8</v>
+        <v>90</v>
       </c>
     </row>
     <row r="475">
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="C505" s="3" t="n">
-        <v>108.45</v>
+        <v>108.95</v>
       </c>
       <c r="D505" s="3" t="n">
         <v>96</v>
@@ -9473,7 +9473,7 @@
         <v>115.45</v>
       </c>
       <c r="D554" s="3" t="n">
-        <v>97.2</v>
+        <v>97</v>
       </c>
     </row>
     <row r="555">
@@ -9489,7 +9489,7 @@
         <v>119.5</v>
       </c>
       <c r="D555" s="3" t="n">
-        <v>100</v>
+        <v>98.05</v>
       </c>
     </row>
     <row r="556">
@@ -9713,7 +9713,7 @@
         <v>110</v>
       </c>
       <c r="D569" s="3" t="n">
-        <v>103.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="570">
@@ -9745,7 +9745,7 @@
         <v>109.95</v>
       </c>
       <c r="D571" s="3" t="n">
-        <v>101.05</v>
+        <v>100.15</v>
       </c>
     </row>
     <row r="572">
@@ -9793,7 +9793,7 @@
         <v>117</v>
       </c>
       <c r="D574" s="3" t="n">
-        <v>105.5</v>
+        <v>105.1</v>
       </c>
     </row>
     <row r="575">
@@ -9809,7 +9809,7 @@
         <v>116.5</v>
       </c>
       <c r="D575" s="3" t="n">
-        <v>106.5</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="576">
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="C627" s="3" t="n">
-        <v>135.75</v>
+        <v>201</v>
       </c>
       <c r="D627" s="3" t="n">
         <v>92</v>
@@ -11262,7 +11262,7 @@
         </is>
       </c>
       <c r="C666" s="3" t="n">
-        <v>150</v>
+        <v>222</v>
       </c>
       <c r="D666" s="3" t="n">
         <v>95.5</v>
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="C667" s="3" t="n">
-        <v>111</v>
+        <v>159</v>
       </c>
       <c r="D667" s="3" t="n">
         <v>100</v>
@@ -11406,7 +11406,7 @@
         </is>
       </c>
       <c r="C675" s="3" t="n">
-        <v>542</v>
+        <v>666</v>
       </c>
       <c r="D675" s="3" t="n">
         <v>111.1</v>
@@ -11726,7 +11726,7 @@
         </is>
       </c>
       <c r="C695" s="3" t="n">
-        <v>104.6</v>
+        <v>106.5</v>
       </c>
       <c r="D695" s="3" t="n">
         <v>99.5</v>
@@ -12350,7 +12350,7 @@
         </is>
       </c>
       <c r="C734" s="3" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D734" s="3" t="n">
         <v>104.05</v>
@@ -12494,7 +12494,7 @@
         </is>
       </c>
       <c r="C743" s="3" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D743" s="3" t="n">
         <v>103.6</v>
@@ -12622,7 +12622,7 @@
         </is>
       </c>
       <c r="C751" s="3" t="n">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="D751" s="3" t="n">
         <v>106.8</v>
@@ -12638,7 +12638,7 @@
         </is>
       </c>
       <c r="C752" s="3" t="n">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="D752" s="3" t="n">
         <v>110.3</v>
@@ -12654,7 +12654,7 @@
         </is>
       </c>
       <c r="C753" s="3" t="n">
-        <v>302</v>
+        <v>454</v>
       </c>
       <c r="D753" s="3" t="n">
         <v>119.5</v>
@@ -12958,7 +12958,7 @@
         </is>
       </c>
       <c r="C772" s="3" t="n">
-        <v>504</v>
+        <v>536</v>
       </c>
       <c r="D772" s="3" t="n">
         <v>113</v>
@@ -13761,7 +13761,7 @@
         <v>121</v>
       </c>
       <c r="D822" s="3" t="n">
-        <v>92.05</v>
+        <v>91.55</v>
       </c>
     </row>
     <row r="823">
@@ -14798,7 +14798,7 @@
         </is>
       </c>
       <c r="C887" s="3" t="n">
-        <v>185</v>
+        <v>275</v>
       </c>
       <c r="D887" s="3" t="n">
         <v>100</v>
@@ -15022,7 +15022,7 @@
         </is>
       </c>
       <c r="C901" s="3" t="n">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="D901" s="3" t="n">
         <v>101.5</v>
@@ -15054,7 +15054,7 @@
         </is>
       </c>
       <c r="C903" s="3" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="D903" s="3" t="n">
         <v>105.1</v>
@@ -15422,7 +15422,7 @@
         </is>
       </c>
       <c r="C926" s="3" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="D926" s="3" t="n">
         <v>100.5</v>
@@ -15710,7 +15710,7 @@
         </is>
       </c>
       <c r="C944" s="3" t="n">
-        <v>120.1</v>
+        <v>133.5</v>
       </c>
       <c r="D944" s="3" t="n">
         <v>97.09999999999999</v>
@@ -15777,7 +15777,7 @@
         <v>159</v>
       </c>
       <c r="D948" s="3" t="n">
-        <v>102.1</v>
+        <v>100.25</v>
       </c>
     </row>
     <row r="949">
@@ -15870,7 +15870,7 @@
         </is>
       </c>
       <c r="C954" s="3" t="n">
-        <v>213</v>
+        <v>256</v>
       </c>
       <c r="D954" s="3" t="n">
         <v>99</v>
@@ -15886,7 +15886,7 @@
         </is>
       </c>
       <c r="C955" s="3" t="n">
-        <v>173</v>
+        <v>207</v>
       </c>
       <c r="D955" s="3" t="n">
         <v>104</v>
@@ -15902,7 +15902,7 @@
         </is>
       </c>
       <c r="C956" s="3" t="n">
-        <v>140.1</v>
+        <v>158</v>
       </c>
       <c r="D956" s="3" t="n">
         <v>105.05</v>
@@ -16033,7 +16033,7 @@
         <v>145.5</v>
       </c>
       <c r="D964" s="3" t="n">
-        <v>116</v>
+        <v>113.8</v>
       </c>
     </row>
     <row r="965">
@@ -16142,7 +16142,7 @@
         </is>
       </c>
       <c r="C971" s="3" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D971" s="3" t="n">
         <v>117.3</v>
@@ -16241,7 +16241,7 @@
         <v>125</v>
       </c>
       <c r="D977" s="3" t="n">
-        <v>95</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="978">
@@ -16350,7 +16350,7 @@
         </is>
       </c>
       <c r="C984" s="3" t="n">
-        <v>243</v>
+        <v>281</v>
       </c>
       <c r="D984" s="3" t="n">
         <v>99</v>
@@ -16366,7 +16366,7 @@
         </is>
       </c>
       <c r="C985" s="3" t="n">
-        <v>255</v>
+        <v>292</v>
       </c>
       <c r="D985" s="3" t="n">
         <v>96</v>
@@ -16414,7 +16414,7 @@
         </is>
       </c>
       <c r="C988" s="3" t="n">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D988" s="3" t="n">
         <v>122</v>
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="C1008" s="3" t="n">
-        <v>115.5</v>
+        <v>116</v>
       </c>
       <c r="D1008" s="3" t="n">
         <v>99.84999999999999</v>
@@ -17214,7 +17214,7 @@
         </is>
       </c>
       <c r="C1038" s="3" t="n">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D1038" s="3" t="n">
         <v>104</v>
@@ -17265,7 +17265,7 @@
         <v>112.9</v>
       </c>
       <c r="D1041" s="3" t="n">
-        <v>95.65000000000001</v>
+        <v>94.05</v>
       </c>
     </row>
     <row r="1042">
@@ -17390,7 +17390,7 @@
         </is>
       </c>
       <c r="C1049" s="3" t="n">
-        <v>127</v>
+        <v>141.95</v>
       </c>
       <c r="D1049" s="3" t="n">
         <v>94.65000000000001</v>
@@ -17502,7 +17502,7 @@
         </is>
       </c>
       <c r="C1056" s="3" t="n">
-        <v>132.8</v>
+        <v>165</v>
       </c>
       <c r="D1056" s="3" t="n">
         <v>93.5</v>
@@ -17518,7 +17518,7 @@
         </is>
       </c>
       <c r="C1057" s="3" t="n">
-        <v>137</v>
+        <v>170</v>
       </c>
       <c r="D1057" s="3" t="n">
         <v>96.05</v>
@@ -17614,7 +17614,7 @@
         </is>
       </c>
       <c r="C1063" s="3" t="n">
-        <v>171</v>
+        <v>232</v>
       </c>
       <c r="D1063" s="3" t="n">
         <v>110.2</v>
@@ -17745,7 +17745,7 @@
         <v>145.5</v>
       </c>
       <c r="D1071" s="3" t="n">
-        <v>130.15</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1072">
@@ -17758,7 +17758,7 @@
         </is>
       </c>
       <c r="C1072" s="3" t="n">
-        <v>135</v>
+        <v>139.9</v>
       </c>
       <c r="D1072" s="3" t="n">
         <v>104.55</v>
@@ -18097,7 +18097,7 @@
         <v>99.95</v>
       </c>
       <c r="D1093" s="3" t="n">
-        <v>89.05</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="1094">
@@ -18913,7 +18913,7 @@
         <v>121.3</v>
       </c>
       <c r="D1144" s="3" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1145">
@@ -19886,7 +19886,7 @@
         </is>
       </c>
       <c r="C1205" s="3" t="n">
-        <v>233</v>
+        <v>332</v>
       </c>
       <c r="D1205" s="3" t="n">
         <v>90</v>
@@ -19998,7 +19998,7 @@
         </is>
       </c>
       <c r="C1212" s="3" t="n">
-        <v>123.5</v>
+        <v>138.9</v>
       </c>
       <c r="D1212" s="3" t="n">
         <v>100</v>
@@ -20049,7 +20049,7 @@
         <v>105</v>
       </c>
       <c r="D1215" s="3" t="n">
-        <v>100</v>
+        <v>99.05</v>
       </c>
     </row>
     <row r="1216">
@@ -20177,7 +20177,7 @@
         <v>121</v>
       </c>
       <c r="D1223" s="3" t="n">
-        <v>103.05</v>
+        <v>100.95</v>
       </c>
     </row>
     <row r="1224">
@@ -20494,7 +20494,7 @@
         </is>
       </c>
       <c r="C1243" s="3" t="n">
-        <v>157</v>
+        <v>206</v>
       </c>
       <c r="D1243" s="3" t="n">
         <v>122.75</v>
@@ -20702,7 +20702,7 @@
         </is>
       </c>
       <c r="C1256" s="3" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D1256" s="3" t="n">
         <v>110.45</v>
@@ -20817,7 +20817,7 @@
         <v>173</v>
       </c>
       <c r="D1263" s="3" t="n">
-        <v>100.85</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="1264">
@@ -21342,7 +21342,7 @@
         </is>
       </c>
       <c r="C1296" s="3" t="n">
-        <v>169</v>
+        <v>207</v>
       </c>
       <c r="D1296" s="3" t="n">
         <v>99</v>
@@ -21374,7 +21374,7 @@
         </is>
       </c>
       <c r="C1298" s="3" t="n">
-        <v>123.45</v>
+        <v>142.35</v>
       </c>
       <c r="D1298" s="3" t="n">
         <v>96.3</v>
@@ -21598,7 +21598,7 @@
         </is>
       </c>
       <c r="C1312" s="3" t="n">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="D1312" s="3" t="n">
         <v>130</v>
@@ -21742,7 +21742,7 @@
         </is>
       </c>
       <c r="C1321" s="3" t="n">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="D1321" s="3" t="n">
         <v>101.5</v>
@@ -21758,7 +21758,7 @@
         </is>
       </c>
       <c r="C1322" s="3" t="n">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="D1322" s="3" t="n">
         <v>99</v>
@@ -22798,7 +22798,7 @@
         </is>
       </c>
       <c r="C1387" s="3" t="n">
-        <v>129.5</v>
+        <v>130</v>
       </c>
       <c r="D1387" s="3" t="n">
         <v>110.3</v>
@@ -23438,7 +23438,7 @@
         </is>
       </c>
       <c r="C1427" s="3" t="n">
-        <v>232</v>
+        <v>260</v>
       </c>
       <c r="D1427" s="3" t="n">
         <v>104.1</v>
@@ -24689,7 +24689,7 @@
         <v>200</v>
       </c>
       <c r="D1505" s="3" t="n">
-        <v>100</v>
+        <v>99.95</v>
       </c>
     </row>
     <row r="1506">
@@ -24734,7 +24734,7 @@
         </is>
       </c>
       <c r="C1508" s="3" t="n">
-        <v>149.9</v>
+        <v>180</v>
       </c>
       <c r="D1508" s="3" t="n">
         <v>97.59999999999999</v>
@@ -24782,7 +24782,7 @@
         </is>
       </c>
       <c r="C1511" s="3" t="n">
-        <v>118</v>
+        <v>118.1</v>
       </c>
       <c r="D1511" s="3" t="n">
         <v>106.5</v>
@@ -24798,7 +24798,7 @@
         </is>
       </c>
       <c r="C1512" s="3" t="n">
-        <v>101</v>
+        <v>104.5</v>
       </c>
       <c r="D1512" s="3" t="n">
         <v>93.40000000000001</v>
@@ -27054,7 +27054,7 @@
         </is>
       </c>
       <c r="C1653" s="3" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D1653" s="3" t="n">
         <v>91</v>
@@ -27070,7 +27070,7 @@
         </is>
       </c>
       <c r="C1654" s="3" t="n">
-        <v>144.95</v>
+        <v>290</v>
       </c>
       <c r="D1654" s="3" t="n">
         <v>85</v>
@@ -27121,7 +27121,7 @@
         <v>120.3</v>
       </c>
       <c r="D1657" s="3" t="n">
-        <v>98</v>
+        <v>97.25</v>
       </c>
     </row>
     <row r="1658">
@@ -27422,7 +27422,7 @@
         </is>
       </c>
       <c r="C1676" s="3" t="n">
-        <v>178</v>
+        <v>218</v>
       </c>
       <c r="D1676" s="3" t="n">
         <v>109</v>
@@ -27614,7 +27614,7 @@
         </is>
       </c>
       <c r="C1688" s="3" t="n">
-        <v>149.6</v>
+        <v>193</v>
       </c>
       <c r="D1688" s="3" t="n">
         <v>101.75</v>
@@ -27870,7 +27870,7 @@
         </is>
       </c>
       <c r="C1704" s="3" t="n">
-        <v>131</v>
+        <v>223</v>
       </c>
       <c r="D1704" s="3" t="n">
         <v>106</v>
@@ -27886,7 +27886,7 @@
         </is>
       </c>
       <c r="C1705" s="3" t="n">
-        <v>132.95</v>
+        <v>228</v>
       </c>
       <c r="D1705" s="3" t="n">
         <v>106.65</v>
@@ -27982,7 +27982,7 @@
         </is>
       </c>
       <c r="C1711" s="3" t="n">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="D1711" s="3" t="n">
         <v>118</v>
@@ -28241,7 +28241,7 @@
         <v>118.45</v>
       </c>
       <c r="D1727" s="3" t="n">
-        <v>103.15</v>
+        <v>102.5</v>
       </c>
     </row>
     <row r="1728">
@@ -29454,7 +29454,7 @@
         </is>
       </c>
       <c r="C1803" s="3" t="n">
-        <v>277</v>
+        <v>450</v>
       </c>
       <c r="D1803" s="3" t="n">
         <v>118.8</v>
@@ -29694,7 +29694,7 @@
         </is>
       </c>
       <c r="C1818" s="3" t="n">
-        <v>133.5</v>
+        <v>156</v>
       </c>
       <c r="D1818" s="3" t="n">
         <v>100.05</v>
@@ -30142,7 +30142,7 @@
         </is>
       </c>
       <c r="C1846" s="3" t="n">
-        <v>130</v>
+        <v>132.5</v>
       </c>
       <c r="D1846" s="3" t="n">
         <v>102</v>
@@ -30190,7 +30190,7 @@
         </is>
       </c>
       <c r="C1849" s="3" t="n">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="D1849" s="3" t="n">
         <v>108.1</v>
@@ -30270,7 +30270,7 @@
         </is>
       </c>
       <c r="C1854" s="3" t="n">
-        <v>140</v>
+        <v>217</v>
       </c>
       <c r="D1854" s="3" t="n">
         <v>100</v>
@@ -30494,7 +30494,7 @@
         </is>
       </c>
       <c r="C1868" s="3" t="n">
-        <v>212</v>
+        <v>268</v>
       </c>
       <c r="D1868" s="3" t="n">
         <v>86.5</v>
@@ -30561,7 +30561,7 @@
         <v>118.5</v>
       </c>
       <c r="D1872" s="3" t="n">
-        <v>99.5</v>
+        <v>98.55</v>
       </c>
     </row>
     <row r="1873">
@@ -30625,7 +30625,7 @@
         <v>108.75</v>
       </c>
       <c r="D1876" s="3" t="n">
-        <v>102.25</v>
+        <v>90.8</v>
       </c>
     </row>
     <row r="1877">
@@ -30638,10 +30638,10 @@
         </is>
       </c>
       <c r="C1877" s="3" t="n">
-        <v>107.8</v>
+        <v>108</v>
       </c>
       <c r="D1877" s="3" t="n">
-        <v>104.5</v>
+        <v>92</v>
       </c>
     </row>
     <row r="1878">
@@ -30705,7 +30705,7 @@
         <v>113</v>
       </c>
       <c r="D1881" s="3" t="n">
-        <v>94</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="1882">
@@ -30846,7 +30846,7 @@
         </is>
       </c>
       <c r="C1890" s="3" t="n">
-        <v>133</v>
+        <v>140.5</v>
       </c>
       <c r="D1890" s="3" t="n">
         <v>99.95</v>
@@ -30942,7 +30942,7 @@
         </is>
       </c>
       <c r="C1896" s="3" t="n">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="D1896" s="3" t="n">
         <v>87.09999999999999</v>
@@ -31086,7 +31086,7 @@
         </is>
       </c>
       <c r="C1905" s="3" t="n">
-        <v>123</v>
+        <v>127.85</v>
       </c>
       <c r="D1905" s="3" t="n">
         <v>105</v>
@@ -31185,7 +31185,7 @@
         <v>191</v>
       </c>
       <c r="D1911" s="3" t="n">
-        <v>100.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1912">
@@ -31265,7 +31265,7 @@
         <v>124</v>
       </c>
       <c r="D1916" s="3" t="n">
-        <v>94.2</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1917">
@@ -31550,7 +31550,7 @@
         </is>
       </c>
       <c r="C1934" s="3" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D1934" s="3" t="n">
         <v>95.55</v>
@@ -31630,7 +31630,7 @@
         </is>
       </c>
       <c r="C1939" s="3" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D1939" s="3" t="n">
         <v>109</v>
@@ -31646,7 +31646,7 @@
         </is>
       </c>
       <c r="C1940" s="3" t="n">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D1940" s="3" t="n">
         <v>101</v>
@@ -31662,7 +31662,7 @@
         </is>
       </c>
       <c r="C1941" s="3" t="n">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="D1941" s="3" t="n">
         <v>100</v>
@@ -31726,7 +31726,7 @@
         </is>
       </c>
       <c r="C1945" s="3" t="n">
-        <v>115.95</v>
+        <v>130.05</v>
       </c>
       <c r="D1945" s="3" t="n">
         <v>88.05</v>
@@ -31758,7 +31758,7 @@
         </is>
       </c>
       <c r="C1947" s="3" t="n">
-        <v>294</v>
+        <v>332</v>
       </c>
       <c r="D1947" s="3" t="n">
         <v>97.5</v>
@@ -31825,7 +31825,7 @@
         <v>172</v>
       </c>
       <c r="D1951" s="3" t="n">
-        <v>101.05</v>
+        <v>101</v>
       </c>
     </row>
     <row r="1952">
@@ -31841,7 +31841,7 @@
         <v>118</v>
       </c>
       <c r="D1952" s="3" t="n">
-        <v>103.25</v>
+        <v>102.1</v>
       </c>
     </row>
     <row r="1953">
@@ -31873,7 +31873,7 @@
         <v>105.5</v>
       </c>
       <c r="D1954" s="3" t="n">
-        <v>90.55</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="1955">
@@ -31921,7 +31921,7 @@
         <v>167</v>
       </c>
       <c r="D1957" s="3" t="n">
-        <v>96.7</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1958">
@@ -31934,7 +31934,7 @@
         </is>
       </c>
       <c r="C1958" s="3" t="n">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="D1958" s="3" t="n">
         <v>100.55</v>
@@ -31966,7 +31966,7 @@
         </is>
       </c>
       <c r="C1960" s="3" t="n">
-        <v>589</v>
+        <v>646</v>
       </c>
       <c r="D1960" s="3" t="n">
         <v>99.84999999999999</v>
@@ -32126,7 +32126,7 @@
         </is>
       </c>
       <c r="C1970" s="3" t="n">
-        <v>113.7</v>
+        <v>114</v>
       </c>
       <c r="D1970" s="3" t="n">
         <v>93</v>
@@ -32142,7 +32142,7 @@
         </is>
       </c>
       <c r="C1971" s="3" t="n">
-        <v>118.5</v>
+        <v>120</v>
       </c>
       <c r="D1971" s="3" t="n">
         <v>94.5</v>
@@ -32209,7 +32209,7 @@
         <v>124.55</v>
       </c>
       <c r="D1975" s="3" t="n">
-        <v>92.75</v>
+        <v>87.09999999999999</v>
       </c>
     </row>
     <row r="1976">
@@ -32225,7 +32225,7 @@
         <v>117.6</v>
       </c>
       <c r="D1976" s="3" t="n">
-        <v>90.8</v>
+        <v>86</v>
       </c>
     </row>
     <row r="1977">
@@ -32270,7 +32270,7 @@
         </is>
       </c>
       <c r="C1979" s="3" t="n">
-        <v>141</v>
+        <v>148.95</v>
       </c>
       <c r="D1979" s="3" t="n">
         <v>111</v>
@@ -32289,7 +32289,7 @@
         <v>122.5</v>
       </c>
       <c r="D1980" s="3" t="n">
-        <v>100.3</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="1981">
@@ -32305,7 +32305,7 @@
         <v>119.5</v>
       </c>
       <c r="D1981" s="3" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="1982">
@@ -32353,7 +32353,7 @@
         <v>168</v>
       </c>
       <c r="D1984" s="3" t="n">
-        <v>121</v>
+        <v>120.7</v>
       </c>
     </row>
     <row r="1985">
@@ -32510,7 +32510,7 @@
         </is>
       </c>
       <c r="C1994" s="3" t="n">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="D1994" s="3" t="n">
         <v>126</v>
@@ -32558,7 +32558,7 @@
         </is>
       </c>
       <c r="C1997" s="3" t="n">
-        <v>265</v>
+        <v>420</v>
       </c>
       <c r="D1997" s="3" t="n">
         <v>101</v>
@@ -32590,7 +32590,7 @@
         </is>
       </c>
       <c r="C1999" s="3" t="n">
-        <v>181</v>
+        <v>237</v>
       </c>
       <c r="D1999" s="3" t="n">
         <v>94</v>
@@ -32750,7 +32750,7 @@
         </is>
       </c>
       <c r="C2009" s="3" t="n">
-        <v>140.5</v>
+        <v>250</v>
       </c>
       <c r="D2009" s="3" t="n">
         <v>103</v>
@@ -33502,7 +33502,7 @@
         </is>
       </c>
       <c r="C2056" s="3" t="n">
-        <v>154</v>
+        <v>210</v>
       </c>
       <c r="D2056" s="3" t="n">
         <v>102</v>
@@ -34126,7 +34126,7 @@
         </is>
       </c>
       <c r="C2095" s="3" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D2095" s="3" t="n">
         <v>94.5</v>
@@ -34142,7 +34142,7 @@
         </is>
       </c>
       <c r="C2096" s="3" t="n">
-        <v>355</v>
+        <v>389</v>
       </c>
       <c r="D2096" s="3" t="n">
         <v>102.05</v>
@@ -34254,7 +34254,7 @@
         </is>
       </c>
       <c r="C2103" s="3" t="n">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="D2103" s="3" t="n">
         <v>110.55</v>
@@ -34270,7 +34270,7 @@
         </is>
       </c>
       <c r="C2104" s="3" t="n">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="D2104" s="3" t="n">
         <v>122.95</v>
@@ -34558,7 +34558,7 @@
         </is>
       </c>
       <c r="C2122" s="3" t="n">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="D2122" s="3" t="n">
         <v>111.1</v>
@@ -34865,7 +34865,7 @@
         <v>123.4</v>
       </c>
       <c r="D2141" s="3" t="n">
-        <v>100.2</v>
+        <v>100.1</v>
       </c>
     </row>
     <row r="2142">
@@ -35041,7 +35041,7 @@
         <v>117</v>
       </c>
       <c r="D2152" s="3" t="n">
-        <v>99.05</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2153">
@@ -35185,7 +35185,7 @@
         <v>158</v>
       </c>
       <c r="D2161" s="3" t="n">
-        <v>99.75</v>
+        <v>99.3</v>
       </c>
     </row>
     <row r="2162">
@@ -36142,7 +36142,7 @@
         </is>
       </c>
       <c r="C2221" s="3" t="n">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="D2221" s="3" t="n">
         <v>107</v>
@@ -36241,7 +36241,7 @@
         <v>142.7</v>
       </c>
       <c r="D2227" s="3" t="n">
-        <v>102.8</v>
+        <v>101.05</v>
       </c>
     </row>
     <row r="2228">
@@ -36769,7 +36769,7 @@
         <v>115</v>
       </c>
       <c r="D2260" s="6" t="n">
-        <v>95.15000000000001</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="2261">
@@ -36958,7 +36958,7 @@
         </is>
       </c>
       <c r="C2272" s="6" t="n">
-        <v>156</v>
+        <v>190</v>
       </c>
       <c r="D2272" s="6" t="n">
         <v>104.1</v>
@@ -36974,7 +36974,7 @@
         </is>
       </c>
       <c r="C2273" s="6" t="n">
-        <v>415</v>
+        <v>468</v>
       </c>
       <c r="D2273" s="6" t="n">
         <v>117.85</v>
@@ -37013,35 +37013,355 @@
       </c>
     </row>
     <row r="2276">
-      <c r="A2276" t="n">
+      <c r="A2276" s="0" t="n">
         <v>81114</v>
       </c>
-      <c r="B2276" t="inlineStr">
+      <c r="B2276" s="0" t="inlineStr">
         <is>
           <t>立�皏|</t>
         </is>
       </c>
-      <c r="C2276" t="n">
+      <c r="C2276" s="0" t="n">
+        <v>134</v>
+      </c>
+      <c r="D2276" s="0" t="n">
+        <v>111.1</v>
+      </c>
+    </row>
+    <row r="2277">
+      <c r="A2277" s="0" t="n">
+        <v>84762</v>
+      </c>
+      <c r="B2277" s="0" t="inlineStr">
+        <is>
+          <t>台境二</t>
+        </is>
+      </c>
+      <c r="C2277" s="0" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="D2277" s="0" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2278">
+      <c r="A2278" t="n">
+        <v>31352</v>
+      </c>
+      <c r="B2278" t="inlineStr">
+        <is>
+          <t>凌航二</t>
+        </is>
+      </c>
+      <c r="C2278" t="n">
+        <v>178</v>
+      </c>
+      <c r="D2278" t="n">
+        <v>122.3</v>
+      </c>
+    </row>
+    <row r="2279">
+      <c r="A2279" t="n">
+        <v>36805</v>
+      </c>
+      <c r="B2279" t="inlineStr">
+        <is>
+          <t>家登五</t>
+        </is>
+      </c>
+      <c r="C2279" t="n">
+        <v>161</v>
+      </c>
+      <c r="D2279" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2280">
+      <c r="A2280" t="n">
+        <v>36806</v>
+      </c>
+      <c r="B2280" t="inlineStr">
+        <is>
+          <t>家登六</t>
+        </is>
+      </c>
+      <c r="C2280" t="n">
+        <v>155</v>
+      </c>
+      <c r="D2280" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2281">
+      <c r="A2281" t="n">
+        <v>41238</v>
+      </c>
+      <c r="B2281" t="inlineStr">
+        <is>
+          <t>晟德八</t>
+        </is>
+      </c>
+      <c r="C2281" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="D2281" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2282">
+      <c r="A2282" t="n">
+        <v>41239</v>
+      </c>
+      <c r="B2282" t="inlineStr">
+        <is>
+          <t>晟德九</t>
+        </is>
+      </c>
+      <c r="C2282" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="D2282" t="n">
+        <v>90.65000000000001</v>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="A2283" t="n">
+        <v>45031</v>
+      </c>
+      <c r="B2283" t="inlineStr">
+        <is>
+          <t>金雨一</t>
+        </is>
+      </c>
+      <c r="C2283" t="n">
+        <v>119.2</v>
+      </c>
+      <c r="D2283" t="n">
+        <v>110.1</v>
+      </c>
+    </row>
+    <row r="2284">
+      <c r="A2284" t="n">
+        <v>47148</v>
+      </c>
+      <c r="B2284" t="inlineStr">
+        <is>
+          <t>永捷八</t>
+        </is>
+      </c>
+      <c r="C2284" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="D2284" t="n">
+        <v>109.25</v>
+      </c>
+    </row>
+    <row r="2285">
+      <c r="A2285" t="n">
+        <v>47224</v>
+      </c>
+      <c r="B2285" t="inlineStr">
+        <is>
+          <t>國精化四</t>
+        </is>
+      </c>
+      <c r="C2285" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="D2285" t="n">
+        <v>112.2</v>
+      </c>
+    </row>
+    <row r="2286">
+      <c r="A2286" t="n">
+        <v>47491</v>
+      </c>
+      <c r="B2286" t="inlineStr">
+        <is>
+          <t>新應材一</t>
+        </is>
+      </c>
+      <c r="C2286" t="n">
+        <v>154</v>
+      </c>
+      <c r="D2286" t="n">
+        <v>148.15</v>
+      </c>
+    </row>
+    <row r="2287">
+      <c r="A2287" t="n">
+        <v>47602</v>
+      </c>
+      <c r="B2287" t="inlineStr">
+        <is>
+          <t>勤凱二</t>
+        </is>
+      </c>
+      <c r="C2287" t="n">
+        <v>177</v>
+      </c>
+      <c r="D2287" t="n">
+        <v>147.1</v>
+      </c>
+    </row>
+    <row r="2288">
+      <c r="A2288" t="n">
+        <v>49311</v>
+      </c>
+      <c r="B2288" t="inlineStr">
+        <is>
+          <t>新盛力一</t>
+        </is>
+      </c>
+      <c r="C2288" t="n">
+        <v>149.4</v>
+      </c>
+      <c r="D2288" t="n">
+        <v>149.4</v>
+      </c>
+    </row>
+    <row r="2289">
+      <c r="A2289" t="n">
+        <v>52844</v>
+      </c>
+      <c r="B2289" t="inlineStr">
+        <is>
+          <t>jpp四KY</t>
+        </is>
+      </c>
+      <c r="C2289" t="n">
+        <v>145.9</v>
+      </c>
+      <c r="D2289" t="n">
+        <v>110.55</v>
+      </c>
+    </row>
+    <row r="2290">
+      <c r="A2290" t="n">
+        <v>52845</v>
+      </c>
+      <c r="B2290" t="inlineStr">
+        <is>
+          <t>jpp五KY</t>
+        </is>
+      </c>
+      <c r="C2290" t="n">
+        <v>154</v>
+      </c>
+      <c r="D2290" t="n">
+        <v>125.1</v>
+      </c>
+    </row>
+    <row r="2291">
+      <c r="A2291" t="n">
+        <v>54642</v>
+      </c>
+      <c r="B2291" t="inlineStr">
+        <is>
+          <t>霖宏二</t>
+        </is>
+      </c>
+      <c r="C2291" t="n">
+        <v>213</v>
+      </c>
+      <c r="D2291" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2292">
+      <c r="A2292" t="n">
+        <v>66034</v>
+      </c>
+      <c r="B2292" t="inlineStr">
+        <is>
+          <t>富強鑫四</t>
+        </is>
+      </c>
+      <c r="C2292" t="n">
+        <v>114</v>
+      </c>
+      <c r="D2292" t="n">
+        <v>104.5</v>
+      </c>
+    </row>
+    <row r="2293">
+      <c r="A2293" t="n">
+        <v>68032</v>
+      </c>
+      <c r="B2293" t="inlineStr">
+        <is>
+          <t>崑鼎二</t>
+        </is>
+      </c>
+      <c r="C2293" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="D2293" t="n">
+        <v>86.09999999999999</v>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="A2294" t="n">
+        <v>76101</v>
+      </c>
+      <c r="B2294" t="inlineStr">
+        <is>
+          <t>聯友金屬一創</t>
+        </is>
+      </c>
+      <c r="C2294" t="n">
+        <v>168</v>
+      </c>
+      <c r="D2294" t="n">
         <v>122.2</v>
       </c>
-      <c r="D2276" t="n">
-        <v>111.1</v>
-      </c>
-    </row>
-    <row r="2277">
-      <c r="A2277" t="n">
-        <v>84762</v>
-      </c>
-      <c r="B2277" t="inlineStr">
-        <is>
-          <t>台境二</t>
-        </is>
-      </c>
-      <c r="C2277" t="n">
-        <v>105.5</v>
-      </c>
-      <c r="D2277" t="n">
-        <v>102</v>
+    </row>
+    <row r="2295">
+      <c r="A2295" t="n">
+        <v>80746</v>
+      </c>
+      <c r="B2295" t="inlineStr">
+        <is>
+          <t>鉅橡六</t>
+        </is>
+      </c>
+      <c r="C2295" t="n">
+        <v>160</v>
+      </c>
+      <c r="D2295" t="n">
+        <v>123.9</v>
+      </c>
+    </row>
+    <row r="2296">
+      <c r="A2296" t="n">
+        <v>82711</v>
+      </c>
+      <c r="B2296" t="inlineStr">
+        <is>
+          <t>宇瞻一</t>
+        </is>
+      </c>
+      <c r="C2296" t="n">
+        <v>167</v>
+      </c>
+      <c r="D2296" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2297">
+      <c r="A2297" t="n">
+        <v>84624</v>
+      </c>
+      <c r="B2297" t="inlineStr">
+        <is>
+          <t>柏文四</t>
+        </is>
+      </c>
+      <c r="C2297" t="n">
+        <v>112.25</v>
+      </c>
+      <c r="D2297" t="n">
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2297"/>
+  <dimension ref="A1:D2323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="7.69140625" bestFit="1" customWidth="1" style="9" min="1" max="1"/>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>94.55</v>
@@ -913,7 +913,7 @@
         <v>125.5</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>102.8</v>
+        <v>99.95</v>
       </c>
     </row>
     <row r="20">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>116.95</v>
+        <v>120</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>103</v>
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>94.25</v>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>99.45</v>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C86" s="3" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="D86" s="3" t="n">
         <v>98.7</v>
@@ -4737,7 +4737,7 @@
         <v>175</v>
       </c>
       <c r="D258" s="3" t="n">
-        <v>111.1</v>
+        <v>111</v>
       </c>
     </row>
     <row r="259">
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="C261" s="3" t="n">
-        <v>123.6</v>
+        <v>158</v>
       </c>
       <c r="D261" s="3" t="n">
         <v>90.5</v>
@@ -4881,7 +4881,7 @@
         <v>119.95</v>
       </c>
       <c r="D267" s="3" t="n">
-        <v>100.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="268">
@@ -5009,7 +5009,7 @@
         <v>135.7</v>
       </c>
       <c r="D275" s="3" t="n">
-        <v>112.2</v>
+        <v>109</v>
       </c>
     </row>
     <row r="276">
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="C301" s="3" t="n">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="D301" s="3" t="n">
         <v>124.15</v>
@@ -7201,7 +7201,7 @@
         <v>135.3</v>
       </c>
       <c r="D412" s="3" t="n">
-        <v>99</v>
+        <v>97.55</v>
       </c>
     </row>
     <row r="413">
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c r="C414" s="3" t="n">
-        <v>233</v>
+        <v>260</v>
       </c>
       <c r="D414" s="3" t="n">
         <v>89.7</v>
@@ -7502,7 +7502,7 @@
         </is>
       </c>
       <c r="C431" s="3" t="n">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="D431" s="3" t="n">
         <v>103.15</v>
@@ -8177,7 +8177,7 @@
         <v>123.5</v>
       </c>
       <c r="D473" s="3" t="n">
-        <v>102</v>
+        <v>101.6</v>
       </c>
     </row>
     <row r="474">
@@ -8257,7 +8257,7 @@
         <v>101.5</v>
       </c>
       <c r="D478" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="479">
@@ -9473,7 +9473,7 @@
         <v>115.45</v>
       </c>
       <c r="D554" s="3" t="n">
-        <v>97</v>
+        <v>95.45</v>
       </c>
     </row>
     <row r="555">
@@ -9745,7 +9745,7 @@
         <v>109.95</v>
       </c>
       <c r="D571" s="3" t="n">
-        <v>100.15</v>
+        <v>100</v>
       </c>
     </row>
     <row r="572">
@@ -9758,7 +9758,7 @@
         </is>
       </c>
       <c r="C572" s="3" t="n">
-        <v>114.9</v>
+        <v>115</v>
       </c>
       <c r="D572" s="3" t="n">
         <v>105.5</v>
@@ -9809,7 +9809,7 @@
         <v>116.5</v>
       </c>
       <c r="D575" s="3" t="n">
-        <v>105.5</v>
+        <v>101.55</v>
       </c>
     </row>
     <row r="576">
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="C627" s="3" t="n">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="D627" s="3" t="n">
         <v>92</v>
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="C667" s="3" t="n">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D667" s="3" t="n">
         <v>100</v>
@@ -11521,7 +11521,7 @@
         <v>157</v>
       </c>
       <c r="D682" s="3" t="n">
-        <v>98.05</v>
+        <v>96.05</v>
       </c>
     </row>
     <row r="683">
@@ -11710,7 +11710,7 @@
         </is>
       </c>
       <c r="C694" s="3" t="n">
-        <v>102</v>
+        <v>104.1</v>
       </c>
       <c r="D694" s="3" t="n">
         <v>97.59999999999999</v>
@@ -11726,7 +11726,7 @@
         </is>
       </c>
       <c r="C695" s="3" t="n">
-        <v>106.5</v>
+        <v>108.8</v>
       </c>
       <c r="D695" s="3" t="n">
         <v>99.5</v>
@@ -12350,7 +12350,7 @@
         </is>
       </c>
       <c r="C734" s="3" t="n">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="D734" s="3" t="n">
         <v>104.05</v>
@@ -12622,7 +12622,7 @@
         </is>
       </c>
       <c r="C751" s="3" t="n">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="D751" s="3" t="n">
         <v>106.8</v>
@@ -12638,7 +12638,7 @@
         </is>
       </c>
       <c r="C752" s="3" t="n">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="D752" s="3" t="n">
         <v>110.3</v>
@@ -12958,7 +12958,7 @@
         </is>
       </c>
       <c r="C772" s="3" t="n">
-        <v>536</v>
+        <v>562</v>
       </c>
       <c r="D772" s="3" t="n">
         <v>113</v>
@@ -13758,10 +13758,10 @@
         </is>
       </c>
       <c r="C822" s="3" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D822" s="3" t="n">
-        <v>91.55</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="823">
@@ -14094,7 +14094,7 @@
         </is>
       </c>
       <c r="C843" s="3" t="n">
-        <v>113</v>
+        <v>115.5</v>
       </c>
       <c r="D843" s="3" t="n">
         <v>95</v>
@@ -14529,7 +14529,7 @@
         <v>148.5</v>
       </c>
       <c r="D870" s="3" t="n">
-        <v>130</v>
+        <v>121.1</v>
       </c>
     </row>
     <row r="871">
@@ -14798,7 +14798,7 @@
         </is>
       </c>
       <c r="C887" s="3" t="n">
-        <v>275</v>
+        <v>324</v>
       </c>
       <c r="D887" s="3" t="n">
         <v>100</v>
@@ -14894,7 +14894,7 @@
         </is>
       </c>
       <c r="C893" s="3" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D893" s="3" t="n">
         <v>110</v>
@@ -15422,7 +15422,7 @@
         </is>
       </c>
       <c r="C926" s="3" t="n">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="D926" s="3" t="n">
         <v>100.5</v>
@@ -16033,7 +16033,7 @@
         <v>145.5</v>
       </c>
       <c r="D964" s="3" t="n">
-        <v>113.8</v>
+        <v>108.5</v>
       </c>
     </row>
     <row r="965">
@@ -16622,7 +16622,7 @@
         </is>
       </c>
       <c r="C1001" s="3" t="n">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="D1001" s="3" t="n">
         <v>97</v>
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="C1008" s="3" t="n">
-        <v>116</v>
+        <v>118.95</v>
       </c>
       <c r="D1008" s="3" t="n">
         <v>99.84999999999999</v>
@@ -17342,7 +17342,7 @@
         </is>
       </c>
       <c r="C1046" s="3" t="n">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="D1046" s="3" t="n">
         <v>115</v>
@@ -17390,7 +17390,7 @@
         </is>
       </c>
       <c r="C1049" s="3" t="n">
-        <v>141.95</v>
+        <v>148</v>
       </c>
       <c r="D1049" s="3" t="n">
         <v>94.65000000000001</v>
@@ -17614,7 +17614,7 @@
         </is>
       </c>
       <c r="C1063" s="3" t="n">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="D1063" s="3" t="n">
         <v>110.2</v>
@@ -17729,7 +17729,7 @@
         <v>161</v>
       </c>
       <c r="D1070" s="3" t="n">
-        <v>111.1</v>
+        <v>107</v>
       </c>
     </row>
     <row r="1071">
@@ -17745,7 +17745,7 @@
         <v>145.5</v>
       </c>
       <c r="D1071" s="3" t="n">
-        <v>126</v>
+        <v>109</v>
       </c>
     </row>
     <row r="1072">
@@ -17758,7 +17758,7 @@
         </is>
       </c>
       <c r="C1072" s="3" t="n">
-        <v>139.9</v>
+        <v>174</v>
       </c>
       <c r="D1072" s="3" t="n">
         <v>104.55</v>
@@ -18081,7 +18081,7 @@
         <v>116.8</v>
       </c>
       <c r="D1092" s="3" t="n">
-        <v>100.7</v>
+        <v>100.55</v>
       </c>
     </row>
     <row r="1093">
@@ -18097,7 +18097,7 @@
         <v>99.95</v>
       </c>
       <c r="D1093" s="3" t="n">
-        <v>85.5</v>
+        <v>85.15000000000001</v>
       </c>
     </row>
     <row r="1094">
@@ -18369,7 +18369,7 @@
         <v>136.75</v>
       </c>
       <c r="D1110" s="3" t="n">
-        <v>97</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="1111">
@@ -18497,7 +18497,7 @@
         <v>130.5</v>
       </c>
       <c r="D1118" s="3" t="n">
-        <v>106</v>
+        <v>105.7</v>
       </c>
     </row>
     <row r="1119">
@@ -18913,7 +18913,7 @@
         <v>121.3</v>
       </c>
       <c r="D1144" s="3" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="1145">
@@ -19009,7 +19009,7 @@
         <v>128</v>
       </c>
       <c r="D1150" s="3" t="n">
-        <v>108</v>
+        <v>107.15</v>
       </c>
     </row>
     <row r="1151">
@@ -19441,7 +19441,7 @@
         <v>144.8</v>
       </c>
       <c r="D1177" s="3" t="n">
-        <v>99.05</v>
+        <v>97.05</v>
       </c>
     </row>
     <row r="1178">
@@ -19537,7 +19537,7 @@
         <v>117</v>
       </c>
       <c r="D1183" s="3" t="n">
-        <v>100.55</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="1184">
@@ -19550,7 +19550,7 @@
         </is>
       </c>
       <c r="C1184" s="3" t="n">
-        <v>108.65</v>
+        <v>108.75</v>
       </c>
       <c r="D1184" s="3" t="n">
         <v>92.84999999999999</v>
@@ -19886,7 +19886,7 @@
         </is>
       </c>
       <c r="C1205" s="3" t="n">
-        <v>332</v>
+        <v>600</v>
       </c>
       <c r="D1205" s="3" t="n">
         <v>90</v>
@@ -20177,7 +20177,7 @@
         <v>121</v>
       </c>
       <c r="D1223" s="3" t="n">
-        <v>100.95</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="1224">
@@ -20494,7 +20494,7 @@
         </is>
       </c>
       <c r="C1243" s="3" t="n">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="D1243" s="3" t="n">
         <v>122.75</v>
@@ -20702,7 +20702,7 @@
         </is>
       </c>
       <c r="C1256" s="3" t="n">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="D1256" s="3" t="n">
         <v>110.45</v>
@@ -21374,7 +21374,7 @@
         </is>
       </c>
       <c r="C1298" s="3" t="n">
-        <v>142.35</v>
+        <v>191</v>
       </c>
       <c r="D1298" s="3" t="n">
         <v>96.3</v>
@@ -22337,7 +22337,7 @@
         <v>197</v>
       </c>
       <c r="D1358" s="3" t="n">
-        <v>102</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="1359">
@@ -22782,10 +22782,10 @@
         </is>
       </c>
       <c r="C1386" s="3" t="n">
-        <v>125.5</v>
+        <v>135.3</v>
       </c>
       <c r="D1386" s="3" t="n">
-        <v>106.5</v>
+        <v>103</v>
       </c>
     </row>
     <row r="1387">
@@ -22798,10 +22798,10 @@
         </is>
       </c>
       <c r="C1387" s="3" t="n">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="D1387" s="3" t="n">
-        <v>110.3</v>
+        <v>110</v>
       </c>
     </row>
     <row r="1388">
@@ -23457,7 +23457,7 @@
         <v>162</v>
       </c>
       <c r="D1428" s="3" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="1429">
@@ -24318,7 +24318,7 @@
         </is>
       </c>
       <c r="C1482" s="3" t="n">
-        <v>128.5</v>
+        <v>132</v>
       </c>
       <c r="D1482" s="3" t="n">
         <v>102.15</v>
@@ -24718,7 +24718,7 @@
         </is>
       </c>
       <c r="C1507" s="3" t="n">
-        <v>133.6</v>
+        <v>147.25</v>
       </c>
       <c r="D1507" s="3" t="n">
         <v>92.7</v>
@@ -24734,7 +24734,7 @@
         </is>
       </c>
       <c r="C1508" s="3" t="n">
-        <v>180</v>
+        <v>235</v>
       </c>
       <c r="D1508" s="3" t="n">
         <v>97.59999999999999</v>
@@ -24782,10 +24782,10 @@
         </is>
       </c>
       <c r="C1511" s="3" t="n">
-        <v>118.1</v>
+        <v>136.2</v>
       </c>
       <c r="D1511" s="3" t="n">
-        <v>106.5</v>
+        <v>105.6</v>
       </c>
     </row>
     <row r="1512">
@@ -24798,7 +24798,7 @@
         </is>
       </c>
       <c r="C1512" s="3" t="n">
-        <v>104.5</v>
+        <v>128</v>
       </c>
       <c r="D1512" s="3" t="n">
         <v>93.40000000000001</v>
@@ -25438,7 +25438,7 @@
         </is>
       </c>
       <c r="C1552" s="3" t="n">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="D1552" s="3" t="n">
         <v>99.59999999999999</v>
@@ -27054,7 +27054,7 @@
         </is>
       </c>
       <c r="C1653" s="3" t="n">
-        <v>159</v>
+        <v>314</v>
       </c>
       <c r="D1653" s="3" t="n">
         <v>91</v>
@@ -27070,7 +27070,7 @@
         </is>
       </c>
       <c r="C1654" s="3" t="n">
-        <v>290</v>
+        <v>574</v>
       </c>
       <c r="D1654" s="3" t="n">
         <v>85</v>
@@ -27121,7 +27121,7 @@
         <v>120.3</v>
       </c>
       <c r="D1657" s="3" t="n">
-        <v>97.25</v>
+        <v>97</v>
       </c>
     </row>
     <row r="1658">
@@ -27422,7 +27422,7 @@
         </is>
       </c>
       <c r="C1676" s="3" t="n">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="D1676" s="3" t="n">
         <v>109</v>
@@ -27614,7 +27614,7 @@
         </is>
       </c>
       <c r="C1688" s="3" t="n">
-        <v>193</v>
+        <v>268</v>
       </c>
       <c r="D1688" s="3" t="n">
         <v>101.75</v>
@@ -27681,7 +27681,7 @@
         <v>130.15</v>
       </c>
       <c r="D1692" s="3" t="n">
-        <v>111.7</v>
+        <v>105.55</v>
       </c>
     </row>
     <row r="1693">
@@ -27870,7 +27870,7 @@
         </is>
       </c>
       <c r="C1704" s="3" t="n">
-        <v>223</v>
+        <v>342</v>
       </c>
       <c r="D1704" s="3" t="n">
         <v>106</v>
@@ -27886,7 +27886,7 @@
         </is>
       </c>
       <c r="C1705" s="3" t="n">
-        <v>228</v>
+        <v>349</v>
       </c>
       <c r="D1705" s="3" t="n">
         <v>106.65</v>
@@ -27982,7 +27982,7 @@
         </is>
       </c>
       <c r="C1711" s="3" t="n">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="D1711" s="3" t="n">
         <v>118</v>
@@ -28241,7 +28241,7 @@
         <v>118.45</v>
       </c>
       <c r="D1727" s="3" t="n">
-        <v>102.5</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="1728">
@@ -29345,7 +29345,7 @@
         <v>111.75</v>
       </c>
       <c r="D1796" s="3" t="n">
-        <v>95</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="1797">
@@ -29454,7 +29454,7 @@
         </is>
       </c>
       <c r="C1803" s="3" t="n">
-        <v>450</v>
+        <v>496</v>
       </c>
       <c r="D1803" s="3" t="n">
         <v>118.8</v>
@@ -29614,7 +29614,7 @@
         </is>
       </c>
       <c r="C1813" s="3" t="n">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="D1813" s="3" t="n">
         <v>95.5</v>
@@ -29694,7 +29694,7 @@
         </is>
       </c>
       <c r="C1818" s="3" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D1818" s="3" t="n">
         <v>100.05</v>
@@ -30142,7 +30142,7 @@
         </is>
       </c>
       <c r="C1846" s="3" t="n">
-        <v>132.5</v>
+        <v>196</v>
       </c>
       <c r="D1846" s="3" t="n">
         <v>102</v>
@@ -30270,7 +30270,7 @@
         </is>
       </c>
       <c r="C1854" s="3" t="n">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="D1854" s="3" t="n">
         <v>100</v>
@@ -30494,7 +30494,7 @@
         </is>
       </c>
       <c r="C1868" s="3" t="n">
-        <v>268</v>
+        <v>306</v>
       </c>
       <c r="D1868" s="3" t="n">
         <v>86.5</v>
@@ -30561,7 +30561,7 @@
         <v>118.5</v>
       </c>
       <c r="D1872" s="3" t="n">
-        <v>98.55</v>
+        <v>97</v>
       </c>
     </row>
     <row r="1873">
@@ -30622,10 +30622,10 @@
         </is>
       </c>
       <c r="C1876" s="3" t="n">
-        <v>108.75</v>
+        <v>109.95</v>
       </c>
       <c r="D1876" s="3" t="n">
-        <v>90.8</v>
+        <v>90.34999999999999</v>
       </c>
     </row>
     <row r="1877">
@@ -30638,7 +30638,7 @@
         </is>
       </c>
       <c r="C1877" s="3" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D1877" s="3" t="n">
         <v>92</v>
@@ -30718,7 +30718,7 @@
         </is>
       </c>
       <c r="C1882" s="3" t="n">
-        <v>98.7</v>
+        <v>103.8</v>
       </c>
       <c r="D1882" s="3" t="n">
         <v>92.05</v>
@@ -30846,7 +30846,7 @@
         </is>
       </c>
       <c r="C1890" s="3" t="n">
-        <v>140.5</v>
+        <v>157</v>
       </c>
       <c r="D1890" s="3" t="n">
         <v>99.95</v>
@@ -30942,7 +30942,7 @@
         </is>
       </c>
       <c r="C1896" s="3" t="n">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="D1896" s="3" t="n">
         <v>87.09999999999999</v>
@@ -31630,7 +31630,7 @@
         </is>
       </c>
       <c r="C1939" s="3" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D1939" s="3" t="n">
         <v>109</v>
@@ -31646,7 +31646,7 @@
         </is>
       </c>
       <c r="C1940" s="3" t="n">
-        <v>250</v>
+        <v>339</v>
       </c>
       <c r="D1940" s="3" t="n">
         <v>101</v>
@@ -31662,7 +31662,7 @@
         </is>
       </c>
       <c r="C1941" s="3" t="n">
-        <v>253</v>
+        <v>333</v>
       </c>
       <c r="D1941" s="3" t="n">
         <v>100</v>
@@ -31681,7 +31681,7 @@
         <v>143.9</v>
       </c>
       <c r="D1942" s="3" t="n">
-        <v>105</v>
+        <v>93</v>
       </c>
     </row>
     <row r="1943">
@@ -31825,7 +31825,7 @@
         <v>172</v>
       </c>
       <c r="D1951" s="3" t="n">
-        <v>101</v>
+        <v>100.05</v>
       </c>
     </row>
     <row r="1952">
@@ -31841,7 +31841,7 @@
         <v>118</v>
       </c>
       <c r="D1952" s="3" t="n">
-        <v>102.1</v>
+        <v>101.6</v>
       </c>
     </row>
     <row r="1953">
@@ -31873,7 +31873,7 @@
         <v>105.5</v>
       </c>
       <c r="D1954" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>86</v>
       </c>
     </row>
     <row r="1955">
@@ -32017,7 +32017,7 @@
         <v>115</v>
       </c>
       <c r="D1963" s="3" t="n">
-        <v>100.65</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1964">
@@ -32081,7 +32081,7 @@
         <v>129.3</v>
       </c>
       <c r="D1967" s="3" t="n">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="1968">
@@ -32126,7 +32126,7 @@
         </is>
       </c>
       <c r="C1970" s="3" t="n">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="D1970" s="3" t="n">
         <v>93</v>
@@ -32142,7 +32142,7 @@
         </is>
       </c>
       <c r="C1971" s="3" t="n">
-        <v>120</v>
+        <v>143.5</v>
       </c>
       <c r="D1971" s="3" t="n">
         <v>94.5</v>
@@ -32254,7 +32254,7 @@
         </is>
       </c>
       <c r="C1978" s="3" t="n">
-        <v>105</v>
+        <v>107.1</v>
       </c>
       <c r="D1978" s="3" t="n">
         <v>99.90000000000001</v>
@@ -32286,7 +32286,7 @@
         </is>
       </c>
       <c r="C1980" s="3" t="n">
-        <v>122.5</v>
+        <v>131.1</v>
       </c>
       <c r="D1980" s="3" t="n">
         <v>98.7</v>
@@ -32510,7 +32510,7 @@
         </is>
       </c>
       <c r="C1994" s="3" t="n">
-        <v>244</v>
+        <v>302</v>
       </c>
       <c r="D1994" s="3" t="n">
         <v>126</v>
@@ -32558,7 +32558,7 @@
         </is>
       </c>
       <c r="C1997" s="3" t="n">
-        <v>420</v>
+        <v>508</v>
       </c>
       <c r="D1997" s="3" t="n">
         <v>101</v>
@@ -32590,7 +32590,7 @@
         </is>
       </c>
       <c r="C1999" s="3" t="n">
-        <v>237</v>
+        <v>262</v>
       </c>
       <c r="D1999" s="3" t="n">
         <v>94</v>
@@ -32750,7 +32750,7 @@
         </is>
       </c>
       <c r="C2009" s="3" t="n">
-        <v>250</v>
+        <v>372</v>
       </c>
       <c r="D2009" s="3" t="n">
         <v>103</v>
@@ -33502,7 +33502,7 @@
         </is>
       </c>
       <c r="C2056" s="3" t="n">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="D2056" s="3" t="n">
         <v>102</v>
@@ -34225,7 +34225,7 @@
         <v>128</v>
       </c>
       <c r="D2101" s="3" t="n">
-        <v>92.05</v>
+        <v>90.8</v>
       </c>
     </row>
     <row r="2102">
@@ -34369,7 +34369,7 @@
         <v>132.5</v>
       </c>
       <c r="D2110" s="3" t="n">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="2111">
@@ -34865,7 +34865,7 @@
         <v>123.4</v>
       </c>
       <c r="D2141" s="3" t="n">
-        <v>100.1</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="2142">
@@ -34926,7 +34926,7 @@
         </is>
       </c>
       <c r="C2145" s="3" t="n">
-        <v>102.3</v>
+        <v>103.2</v>
       </c>
       <c r="D2145" s="3" t="n">
         <v>99.3</v>
@@ -35041,7 +35041,7 @@
         <v>117</v>
       </c>
       <c r="D2152" s="3" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2153">
@@ -35313,7 +35313,7 @@
         <v>178</v>
       </c>
       <c r="D2169" s="3" t="n">
-        <v>106.5</v>
+        <v>104.05</v>
       </c>
     </row>
     <row r="2170">
@@ -35681,7 +35681,7 @@
         <v>136</v>
       </c>
       <c r="D2192" s="3" t="n">
-        <v>100.75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2193">
@@ -36142,7 +36142,7 @@
         </is>
       </c>
       <c r="C2221" s="3" t="n">
-        <v>510</v>
+        <v>530</v>
       </c>
       <c r="D2221" s="3" t="n">
         <v>107</v>
@@ -36241,7 +36241,7 @@
         <v>142.7</v>
       </c>
       <c r="D2227" s="3" t="n">
-        <v>101.05</v>
+        <v>100.5</v>
       </c>
     </row>
     <row r="2228">
@@ -36974,7 +36974,7 @@
         </is>
       </c>
       <c r="C2273" s="6" t="n">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="D2273" s="6" t="n">
         <v>117.85</v>
@@ -36990,7 +36990,7 @@
         </is>
       </c>
       <c r="C2274" s="6" t="n">
-        <v>134</v>
+        <v>141.5</v>
       </c>
       <c r="D2274" s="6" t="n">
         <v>92</v>
@@ -37006,7 +37006,7 @@
         </is>
       </c>
       <c r="C2275" s="6" t="n">
-        <v>111.3</v>
+        <v>123.95</v>
       </c>
       <c r="D2275" s="6" t="n">
         <v>98</v>
@@ -37025,7 +37025,7 @@
         <v>134</v>
       </c>
       <c r="D2276" s="0" t="n">
-        <v>111.1</v>
+        <v>101.85</v>
       </c>
     </row>
     <row r="2277">
@@ -37038,330 +37038,746 @@
         </is>
       </c>
       <c r="C2277" s="0" t="n">
-        <v>105.5</v>
+        <v>124.95</v>
       </c>
       <c r="D2277" s="0" t="n">
         <v>88</v>
       </c>
     </row>
     <row r="2278">
-      <c r="A2278" t="n">
+      <c r="A2278" s="0" t="n">
         <v>31352</v>
       </c>
-      <c r="B2278" t="inlineStr">
+      <c r="B2278" s="0" t="inlineStr">
         <is>
           <t>凌航二</t>
         </is>
       </c>
-      <c r="C2278" t="n">
+      <c r="C2278" s="0" t="n">
         <v>178</v>
       </c>
-      <c r="D2278" t="n">
-        <v>122.3</v>
+      <c r="D2278" s="0" t="n">
+        <v>117</v>
       </c>
     </row>
     <row r="2279">
-      <c r="A2279" t="n">
+      <c r="A2279" s="0" t="n">
         <v>36805</v>
       </c>
-      <c r="B2279" t="inlineStr">
+      <c r="B2279" s="0" t="inlineStr">
         <is>
           <t>家登五</t>
         </is>
       </c>
-      <c r="C2279" t="n">
+      <c r="C2279" s="0" t="n">
         <v>161</v>
       </c>
-      <c r="D2279" t="n">
+      <c r="D2279" s="0" t="n">
         <v>110</v>
       </c>
     </row>
     <row r="2280">
-      <c r="A2280" t="n">
+      <c r="A2280" s="0" t="n">
         <v>36806</v>
       </c>
-      <c r="B2280" t="inlineStr">
+      <c r="B2280" s="0" t="inlineStr">
         <is>
           <t>家登六</t>
         </is>
       </c>
-      <c r="C2280" t="n">
+      <c r="C2280" s="0" t="n">
         <v>155</v>
       </c>
-      <c r="D2280" t="n">
-        <v>144</v>
+      <c r="D2280" s="0" t="n">
+        <v>121</v>
       </c>
     </row>
     <row r="2281">
-      <c r="A2281" t="n">
+      <c r="A2281" s="0" t="n">
         <v>41238</v>
       </c>
-      <c r="B2281" t="inlineStr">
+      <c r="B2281" s="0" t="inlineStr">
         <is>
           <t>晟德八</t>
         </is>
       </c>
-      <c r="C2281" t="n">
+      <c r="C2281" s="0" t="n">
         <v>97.90000000000001</v>
       </c>
-      <c r="D2281" t="n">
-        <v>90</v>
+      <c r="D2281" s="0" t="n">
+        <v>89.5</v>
       </c>
     </row>
     <row r="2282">
-      <c r="A2282" t="n">
+      <c r="A2282" s="0" t="n">
         <v>41239</v>
       </c>
-      <c r="B2282" t="inlineStr">
+      <c r="B2282" s="0" t="inlineStr">
         <is>
           <t>晟德九</t>
         </is>
       </c>
-      <c r="C2282" t="n">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="D2282" t="n">
+      <c r="C2282" s="0" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="D2282" s="0" t="n">
         <v>90.65000000000001</v>
       </c>
     </row>
     <row r="2283">
-      <c r="A2283" t="n">
+      <c r="A2283" s="0" t="n">
         <v>45031</v>
       </c>
-      <c r="B2283" t="inlineStr">
+      <c r="B2283" s="0" t="inlineStr">
         <is>
           <t>金雨一</t>
         </is>
       </c>
-      <c r="C2283" t="n">
-        <v>119.2</v>
-      </c>
-      <c r="D2283" t="n">
+      <c r="C2283" s="0" t="n">
+        <v>124</v>
+      </c>
+      <c r="D2283" s="0" t="n">
         <v>110.1</v>
       </c>
     </row>
     <row r="2284">
-      <c r="A2284" t="n">
+      <c r="A2284" s="0" t="n">
         <v>47148</v>
       </c>
-      <c r="B2284" t="inlineStr">
+      <c r="B2284" s="0" t="inlineStr">
         <is>
           <t>永捷八</t>
         </is>
       </c>
-      <c r="C2284" t="n">
+      <c r="C2284" s="0" t="n">
         <v>116.6</v>
       </c>
-      <c r="D2284" t="n">
-        <v>109.25</v>
+      <c r="D2284" s="0" t="n">
+        <v>106</v>
       </c>
     </row>
     <row r="2285">
-      <c r="A2285" t="n">
+      <c r="A2285" s="0" t="n">
         <v>47224</v>
       </c>
-      <c r="B2285" t="inlineStr">
+      <c r="B2285" s="0" t="inlineStr">
         <is>
           <t>國精化四</t>
         </is>
       </c>
-      <c r="C2285" t="n">
-        <v>136.5</v>
-      </c>
-      <c r="D2285" t="n">
-        <v>112.2</v>
+      <c r="C2285" s="0" t="n">
+        <v>141.55</v>
+      </c>
+      <c r="D2285" s="0" t="n">
+        <v>105</v>
       </c>
     </row>
     <row r="2286">
-      <c r="A2286" t="n">
+      <c r="A2286" s="0" t="n">
         <v>47491</v>
       </c>
-      <c r="B2286" t="inlineStr">
+      <c r="B2286" s="0" t="inlineStr">
         <is>
           <t>新應材一</t>
         </is>
       </c>
-      <c r="C2286" t="n">
+      <c r="C2286" s="0" t="n">
+        <v>165</v>
+      </c>
+      <c r="D2286" s="0" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2287">
+      <c r="A2287" s="0" t="n">
+        <v>47602</v>
+      </c>
+      <c r="B2287" s="0" t="inlineStr">
+        <is>
+          <t>勤凱二</t>
+        </is>
+      </c>
+      <c r="C2287" s="0" t="n">
+        <v>177</v>
+      </c>
+      <c r="D2287" s="0" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2288">
+      <c r="A2288" s="0" t="n">
+        <v>49311</v>
+      </c>
+      <c r="B2288" s="0" t="inlineStr">
+        <is>
+          <t>新盛力一</t>
+        </is>
+      </c>
+      <c r="C2288" s="0" t="n">
+        <v>193</v>
+      </c>
+      <c r="D2288" s="0" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2289">
+      <c r="A2289" s="0" t="n">
+        <v>52844</v>
+      </c>
+      <c r="B2289" s="0" t="inlineStr">
+        <is>
+          <t>jpp四KY</t>
+        </is>
+      </c>
+      <c r="C2289" s="0" t="n">
+        <v>145.9</v>
+      </c>
+      <c r="D2289" s="0" t="n">
+        <v>103.7</v>
+      </c>
+    </row>
+    <row r="2290">
+      <c r="A2290" s="0" t="n">
+        <v>52845</v>
+      </c>
+      <c r="B2290" s="0" t="inlineStr">
+        <is>
+          <t>jpp五KY</t>
+        </is>
+      </c>
+      <c r="C2290" s="0" t="n">
         <v>154</v>
       </c>
-      <c r="D2286" t="n">
-        <v>148.15</v>
-      </c>
-    </row>
-    <row r="2287">
-      <c r="A2287" t="n">
-        <v>47602</v>
-      </c>
-      <c r="B2287" t="inlineStr">
-        <is>
-          <t>勤凱二</t>
-        </is>
-      </c>
-      <c r="C2287" t="n">
-        <v>177</v>
-      </c>
-      <c r="D2287" t="n">
-        <v>147.1</v>
-      </c>
-    </row>
-    <row r="2288">
-      <c r="A2288" t="n">
-        <v>49311</v>
-      </c>
-      <c r="B2288" t="inlineStr">
-        <is>
-          <t>新盛力一</t>
-        </is>
-      </c>
-      <c r="C2288" t="n">
-        <v>149.4</v>
-      </c>
-      <c r="D2288" t="n">
-        <v>149.4</v>
-      </c>
-    </row>
-    <row r="2289">
-      <c r="A2289" t="n">
-        <v>52844</v>
-      </c>
-      <c r="B2289" t="inlineStr">
-        <is>
-          <t>jpp四KY</t>
-        </is>
-      </c>
-      <c r="C2289" t="n">
-        <v>145.9</v>
-      </c>
-      <c r="D2289" t="n">
+      <c r="D2290" s="0" t="n">
+        <v>115.25</v>
+      </c>
+    </row>
+    <row r="2291">
+      <c r="A2291" s="0" t="n">
+        <v>54642</v>
+      </c>
+      <c r="B2291" s="0" t="inlineStr">
+        <is>
+          <t>霖宏二</t>
+        </is>
+      </c>
+      <c r="C2291" s="0" t="n">
+        <v>299</v>
+      </c>
+      <c r="D2291" s="0" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2292">
+      <c r="A2292" s="0" t="n">
+        <v>66034</v>
+      </c>
+      <c r="B2292" s="0" t="inlineStr">
+        <is>
+          <t>富強鑫四</t>
+        </is>
+      </c>
+      <c r="C2292" s="0" t="n">
+        <v>114</v>
+      </c>
+      <c r="D2292" s="0" t="n">
+        <v>104.5</v>
+      </c>
+    </row>
+    <row r="2293">
+      <c r="A2293" s="0" t="n">
+        <v>68032</v>
+      </c>
+      <c r="B2293" s="0" t="inlineStr">
+        <is>
+          <t>崑鼎二</t>
+        </is>
+      </c>
+      <c r="C2293" s="0" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="D2293" s="0" t="n">
+        <v>86.09999999999999</v>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="A2294" s="0" t="n">
+        <v>76101</v>
+      </c>
+      <c r="B2294" s="0" t="inlineStr">
+        <is>
+          <t>聯友金屬一創</t>
+        </is>
+      </c>
+      <c r="C2294" s="0" t="n">
+        <v>361</v>
+      </c>
+      <c r="D2294" s="0" t="n">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="2295">
+      <c r="A2295" s="0" t="n">
+        <v>80746</v>
+      </c>
+      <c r="B2295" s="0" t="inlineStr">
+        <is>
+          <t>鉅橡六</t>
+        </is>
+      </c>
+      <c r="C2295" s="0" t="n">
+        <v>160</v>
+      </c>
+      <c r="D2295" s="0" t="n">
+        <v>105.5</v>
+      </c>
+    </row>
+    <row r="2296">
+      <c r="A2296" s="0" t="n">
+        <v>82711</v>
+      </c>
+      <c r="B2296" s="0" t="inlineStr">
+        <is>
+          <t>宇瞻一</t>
+        </is>
+      </c>
+      <c r="C2296" s="0" t="n">
+        <v>167</v>
+      </c>
+      <c r="D2296" s="0" t="n">
+        <v>125.9</v>
+      </c>
+    </row>
+    <row r="2297">
+      <c r="A2297" s="0" t="n">
+        <v>84624</v>
+      </c>
+      <c r="B2297" s="0" t="inlineStr">
+        <is>
+          <t>柏文四</t>
+        </is>
+      </c>
+      <c r="C2297" s="0" t="n">
+        <v>121.1</v>
+      </c>
+      <c r="D2297" s="0" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2298">
+      <c r="A2298" s="0" t="n">
+        <v>17172</v>
+      </c>
+      <c r="B2298" s="0" t="inlineStr">
+        <is>
+          <t>長興二</t>
+        </is>
+      </c>
+      <c r="C2298" s="0" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="D2298" s="0" t="n">
+        <v>122.55</v>
+      </c>
+    </row>
+    <row r="2299">
+      <c r="A2299" s="0" t="n">
+        <v>32943</v>
+      </c>
+      <c r="B2299" s="0" t="inlineStr">
+        <is>
+          <t>英濟三</t>
+        </is>
+      </c>
+      <c r="C2299" s="0" t="n">
+        <v>131.55</v>
+      </c>
+      <c r="D2299" s="0" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2300">
+      <c r="A2300" s="0" t="n">
+        <v>34913</v>
+      </c>
+      <c r="B2300" s="0" t="inlineStr">
+        <is>
+          <t>昇達科三</t>
+        </is>
+      </c>
+      <c r="C2300" s="0" t="n">
+        <v>160</v>
+      </c>
+      <c r="D2300" s="0" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2301">
+      <c r="A2301" s="0" t="n">
+        <v>41904</v>
+      </c>
+      <c r="B2301" s="0" t="inlineStr">
+        <is>
+          <t>佐登四KY</t>
+        </is>
+      </c>
+      <c r="C2301" s="0" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="D2301" s="0" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2302">
+      <c r="A2302" s="0" t="n">
+        <v>622010</v>
+      </c>
+      <c r="B2302" s="0" t="inlineStr">
+        <is>
+          <t>岳豐十</t>
+        </is>
+      </c>
+      <c r="C2302" s="0" t="n">
+        <v>132</v>
+      </c>
+      <c r="D2302" s="0" t="n">
+        <v>113.85</v>
+      </c>
+    </row>
+    <row r="2303">
+      <c r="A2303" s="0" t="n">
+        <v>62236</v>
+      </c>
+      <c r="B2303" s="0" t="inlineStr">
+        <is>
+          <t>旺矽六</t>
+        </is>
+      </c>
+      <c r="C2303" s="0" t="n">
+        <v>163</v>
+      </c>
+      <c r="D2303" s="0" t="n">
         <v>110.55</v>
       </c>
     </row>
-    <row r="2290">
-      <c r="A2290" t="n">
-        <v>52845</v>
-      </c>
-      <c r="B2290" t="inlineStr">
-        <is>
-          <t>jpp五KY</t>
-        </is>
-      </c>
-      <c r="C2290" t="n">
-        <v>154</v>
-      </c>
-      <c r="D2290" t="n">
-        <v>125.1</v>
-      </c>
-    </row>
-    <row r="2291">
-      <c r="A2291" t="n">
-        <v>54642</v>
-      </c>
-      <c r="B2291" t="inlineStr">
-        <is>
-          <t>霖宏二</t>
-        </is>
-      </c>
-      <c r="C2291" t="n">
-        <v>213</v>
-      </c>
-      <c r="D2291" t="n">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="2292">
-      <c r="A2292" t="n">
-        <v>66034</v>
-      </c>
-      <c r="B2292" t="inlineStr">
-        <is>
-          <t>富強鑫四</t>
-        </is>
-      </c>
-      <c r="C2292" t="n">
-        <v>114</v>
-      </c>
-      <c r="D2292" t="n">
-        <v>104.5</v>
-      </c>
-    </row>
-    <row r="2293">
-      <c r="A2293" t="n">
-        <v>68032</v>
-      </c>
-      <c r="B2293" t="inlineStr">
-        <is>
-          <t>崑鼎二</t>
-        </is>
-      </c>
-      <c r="C2293" t="n">
-        <v>92.59999999999999</v>
-      </c>
-      <c r="D2293" t="n">
-        <v>86.09999999999999</v>
-      </c>
-    </row>
-    <row r="2294">
-      <c r="A2294" t="n">
-        <v>76101</v>
-      </c>
-      <c r="B2294" t="inlineStr">
-        <is>
-          <t>聯友金屬一創</t>
-        </is>
-      </c>
-      <c r="C2294" t="n">
-        <v>168</v>
-      </c>
-      <c r="D2294" t="n">
-        <v>122.2</v>
-      </c>
-    </row>
-    <row r="2295">
-      <c r="A2295" t="n">
-        <v>80746</v>
-      </c>
-      <c r="B2295" t="inlineStr">
-        <is>
-          <t>鉅橡六</t>
-        </is>
-      </c>
-      <c r="C2295" t="n">
-        <v>160</v>
-      </c>
-      <c r="D2295" t="n">
-        <v>123.9</v>
-      </c>
-    </row>
-    <row r="2296">
-      <c r="A2296" t="n">
-        <v>82711</v>
-      </c>
-      <c r="B2296" t="inlineStr">
-        <is>
-          <t>宇瞻一</t>
-        </is>
-      </c>
-      <c r="C2296" t="n">
-        <v>167</v>
-      </c>
-      <c r="D2296" t="n">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="2297">
-      <c r="A2297" t="n">
-        <v>84624</v>
-      </c>
-      <c r="B2297" t="inlineStr">
-        <is>
-          <t>柏文四</t>
-        </is>
-      </c>
-      <c r="C2297" t="n">
-        <v>112.25</v>
-      </c>
-      <c r="D2297" t="n">
-        <v>107</v>
+    <row r="2304">
+      <c r="A2304" s="0" t="n">
+        <v>65462</v>
+      </c>
+      <c r="B2304" s="0" t="inlineStr">
+        <is>
+          <t>正基二</t>
+        </is>
+      </c>
+      <c r="C2304" s="0" t="n">
+        <v>115</v>
+      </c>
+      <c r="D2304" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2305">
+      <c r="A2305" s="0" t="n">
+        <v>65463</v>
+      </c>
+      <c r="B2305" s="0" t="inlineStr">
+        <is>
+          <t>正基三</t>
+        </is>
+      </c>
+      <c r="C2305" s="0" t="n">
+        <v>109</v>
+      </c>
+      <c r="D2305" s="0" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2306">
+      <c r="A2306" s="0" t="n">
+        <v>811211</v>
+      </c>
+      <c r="B2306" s="0" t="inlineStr">
+        <is>
+          <t>至上11</t>
+        </is>
+      </c>
+      <c r="C2306" s="0" t="n">
+        <v>115.85</v>
+      </c>
+      <c r="D2306" s="0" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2307">
+      <c r="A2307" t="n">
+        <v>16231</v>
+      </c>
+      <c r="B2307" t="inlineStr">
+        <is>
+          <t>大東電一</t>
+        </is>
+      </c>
+      <c r="C2307" t="n">
+        <v>112</v>
+      </c>
+      <c r="D2307" t="n">
+        <v>105.5</v>
+      </c>
+    </row>
+    <row r="2308">
+      <c r="A2308" t="n">
+        <v>24867</v>
+      </c>
+      <c r="B2308" t="inlineStr">
+        <is>
+          <t>一詮七</t>
+        </is>
+      </c>
+      <c r="C2308" t="n">
+        <v>132</v>
+      </c>
+      <c r="D2308" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2309">
+      <c r="A2309" t="n">
+        <v>30285</v>
+      </c>
+      <c r="B2309" t="inlineStr">
+        <is>
+          <t>增你強五</t>
+        </is>
+      </c>
+      <c r="C2309" t="n">
+        <v>110</v>
+      </c>
+      <c r="D2309" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2310">
+      <c r="A2310" t="n">
+        <v>35833</v>
+      </c>
+      <c r="B2310" t="inlineStr">
+        <is>
+          <t>辛耘三</t>
+        </is>
+      </c>
+      <c r="C2310" t="n">
+        <v>121</v>
+      </c>
+      <c r="D2310" t="n">
+        <v>113.1</v>
+      </c>
+    </row>
+    <row r="2311">
+      <c r="A2311" t="n">
+        <v>36054</v>
+      </c>
+      <c r="B2311" t="inlineStr">
+        <is>
+          <t>宏致四</t>
+        </is>
+      </c>
+      <c r="C2311" t="n">
+        <v>133.75</v>
+      </c>
+      <c r="D2311" t="n">
+        <v>110.55</v>
+      </c>
+    </row>
+    <row r="2312">
+      <c r="A2312" t="n">
+        <v>52892</v>
+      </c>
+      <c r="B2312" t="inlineStr">
+        <is>
+          <t>宜鼎二</t>
+        </is>
+      </c>
+      <c r="C2312" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="D2312" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2313">
+      <c r="A2313" t="n">
+        <v>52912</v>
+      </c>
+      <c r="B2313" t="inlineStr">
+        <is>
+          <t>邑昇二</t>
+        </is>
+      </c>
+      <c r="C2313" t="n">
+        <v>111</v>
+      </c>
+      <c r="D2313" t="n">
+        <v>108.55</v>
+      </c>
+    </row>
+    <row r="2314">
+      <c r="A2314" t="n">
+        <v>61343</v>
+      </c>
+      <c r="B2314" t="inlineStr">
+        <is>
+          <t>萬旭三</t>
+        </is>
+      </c>
+      <c r="C2314" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="D2314" t="n">
+        <v>118.8</v>
+      </c>
+    </row>
+    <row r="2315">
+      <c r="A2315" t="n">
+        <v>61876</v>
+      </c>
+      <c r="B2315" t="inlineStr">
+        <is>
+          <t>萬潤六</t>
+        </is>
+      </c>
+      <c r="C2315" t="n">
+        <v>141</v>
+      </c>
+      <c r="D2315" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2316">
+      <c r="A2316" t="n">
+        <v>65843</v>
+      </c>
+      <c r="B2316" t="inlineStr">
+        <is>
+          <t>南俊國際三</t>
+        </is>
+      </c>
+      <c r="C2316" t="n">
+        <v>148</v>
+      </c>
+      <c r="D2316" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2317">
+      <c r="A2317" t="n">
+        <v>66931</v>
+      </c>
+      <c r="B2317" t="inlineStr">
+        <is>
+          <t>廣閎科一</t>
+        </is>
+      </c>
+      <c r="C2317" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="D2317" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2318">
+      <c r="A2318" t="n">
+        <v>68692</v>
+      </c>
+      <c r="B2318" t="inlineStr">
+        <is>
+          <t>雲豹能源二</t>
+        </is>
+      </c>
+      <c r="C2318" t="n">
+        <v>111.95</v>
+      </c>
+      <c r="D2318" t="n">
+        <v>106.1</v>
+      </c>
+    </row>
+    <row r="2319">
+      <c r="A2319" t="n">
+        <v>69031</v>
+      </c>
+      <c r="B2319" t="inlineStr">
+        <is>
+          <t>巨漢一</t>
+        </is>
+      </c>
+      <c r="C2319" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="D2319" t="n">
+        <v>106.5</v>
+      </c>
+    </row>
+    <row r="2320">
+      <c r="A2320" t="n">
+        <v>80541</v>
+      </c>
+      <c r="B2320" t="inlineStr">
+        <is>
+          <t>安國一</t>
+        </is>
+      </c>
+      <c r="C2320" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="D2320" t="n">
+        <v>115.5</v>
+      </c>
+    </row>
+    <row r="2321">
+      <c r="A2321" t="n">
+        <v>80962</v>
+      </c>
+      <c r="B2321" t="inlineStr">
+        <is>
+          <t>擎亞二</t>
+        </is>
+      </c>
+      <c r="C2321" t="n">
+        <v>126</v>
+      </c>
+      <c r="D2321" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2322">
+      <c r="A2322" t="n">
+        <v>80963</v>
+      </c>
+      <c r="B2322" t="inlineStr">
+        <is>
+          <t>擎亞三</t>
+        </is>
+      </c>
+      <c r="C2322" t="n">
+        <v>118</v>
+      </c>
+      <c r="D2322" t="n">
+        <v>105.05</v>
+      </c>
+    </row>
+    <row r="2323">
+      <c r="A2323" t="n">
+        <v>84423</v>
+      </c>
+      <c r="B2323" t="inlineStr">
+        <is>
+          <t>威宏三KY</t>
+        </is>
+      </c>
+      <c r="C2323" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="D2323" t="n">
+        <v>111.85</v>
       </c>
     </row>
   </sheetData>
